--- a/Participation/R/output/scenarios/scenario_dynamic_same_months_delta_pp.xlsx
+++ b/Participation/R/output/scenarios/scenario_dynamic_same_months_delta_pp.xlsx
@@ -359,13 +359,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -376,50 +376,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>anchor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>months_block</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>window_days</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>base_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>base_lat_mean</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_start</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_end</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_lat_mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dissim_lat</t>
         </is>
@@ -433,36 +438,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>MSQD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>10-11-12</t>
         </is>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>60</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>41940</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>41999</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>42.9935670194469</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>42644</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>42703</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>40.66164003948874</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>2.331926979958155</v>
       </c>
     </row>
@@ -474,36 +484,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>MSQD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>10-11-12</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>60</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>41940</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>41999</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>42.9935670194469</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>42644</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>42703</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>40.66164003948874</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>2.331926979958155</v>
       </c>
     </row>
@@ -515,36 +530,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>MSQD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>10-11-12</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>60</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>41940</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>41999</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>42.9935670194469</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>42644</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>42703</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>40.66164003948874</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>2.331926979958155</v>
       </c>
     </row>
@@ -556,36 +576,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>MSQD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>10-11-12</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>60</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>41940</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>41999</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>42.9935670194469</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>42644</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>42703</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>40.66164003948874</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>2.331926979958155</v>
       </c>
     </row>
@@ -596,7 +621,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -620,6 +645,11 @@
           <t>delta_pp</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -640,6 +670,11 @@
       <c r="D2">
         <v>5.999871809989505</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,6 +695,11 @@
       <c r="D3">
         <v>4.177771891224213</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -680,6 +720,11 @@
       <c r="D4">
         <v>-0.6431749747037461</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -699,6 +744,11 @@
       </c>
       <c r="D5">
         <v>1.901787694413853</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -708,7 +758,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -732,6 +782,11 @@
           <t>delta_pp</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -752,6 +807,11 @@
       <c r="D2">
         <v>8.436362571664679</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -772,6 +832,11 @@
       <c r="D3">
         <v>-2.155757574447317</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -792,6 +857,11 @@
       <c r="D4">
         <v>-0.2447263563367457</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -812,6 +882,11 @@
       <c r="D5">
         <v>-0.09311114185439713</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -832,6 +907,11 @@
       <c r="D6">
         <v>0.06342100990249441</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -852,6 +932,11 @@
       <c r="D7">
         <v>-0.006316698939203599</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -872,6 +957,11 @@
       <c r="D8">
         <v>4.525357620328255</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -892,6 +982,11 @@
       <c r="D9">
         <v>-0.3060489349346238</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -912,6 +1007,11 @@
       <c r="D10">
         <v>-0.06463727901203625</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -932,6 +1032,11 @@
       <c r="D11">
         <v>0.03683172235916096</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -952,6 +1057,11 @@
       <c r="D12">
         <v>-0.01029042684541695</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -972,6 +1082,11 @@
       <c r="D13">
         <v>-0.003440810671121147</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,6 +1107,11 @@
       <c r="D14">
         <v>-0.3804137288268928</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1012,6 +1132,11 @@
       <c r="D15">
         <v>-0.3470395972402535</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1032,6 +1157,11 @@
       <c r="D16">
         <v>0.06302032592513056</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1182,11 @@
       <c r="D17">
         <v>0.01502547140204979</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1072,6 +1207,11 @@
       <c r="D18">
         <v>0.006232554036223088</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1092,6 +1232,11 @@
       <c r="D19">
         <v>4.9778483174272</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1112,6 +1257,11 @@
       <c r="D20">
         <v>-1.882612624427976</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1132,6 +1282,11 @@
       <c r="D21">
         <v>-0.814586941543163</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1152,6 +1307,11 @@
       <c r="D22">
         <v>-0.3874854547119735</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1171,6 +1331,11 @@
       </c>
       <c r="D23">
         <v>0.008624397669770292</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1204,6 +1369,11 @@
           <t>delta_pp</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1224,6 +1394,11 @@
       <c r="D2">
         <v>5.826668789121178</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1244,6 +1419,11 @@
       <c r="D3">
         <v>-0.6356342119827705</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1264,6 +1444,11 @@
       <c r="D4">
         <v>0.3813631922080097</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1284,6 +1469,11 @@
       <c r="D5">
         <v>0.2215989750704636</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1304,6 +1494,11 @@
       <c r="D6">
         <v>0.2058750655726225</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1324,6 +1519,11 @@
       <c r="D7">
         <v>3.374009836680028</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1344,6 +1544,11 @@
       <c r="D8">
         <v>0.2959267827065523</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1364,6 +1569,11 @@
       <c r="D9">
         <v>0.264410245243072</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1384,6 +1594,11 @@
       <c r="D10">
         <v>0.1736366024961048</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1404,6 +1619,11 @@
       <c r="D11">
         <v>0.1258185114468804</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1424,6 +1644,11 @@
       <c r="D12">
         <v>-0.03891909566492886</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1444,6 +1669,11 @@
       <c r="D13">
         <v>-0.02420459759705854</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1464,6 +1694,11 @@
       <c r="D14">
         <v>0.01247320770416402</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1484,6 +1719,11 @@
       <c r="D15">
         <v>-0.0112096053742114</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1504,6 +1744,11 @@
       <c r="D16">
         <v>0.005830003583613582</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1524,6 +1769,11 @@
       <c r="D17">
         <v>-0.5746153156065124</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1544,6 +1794,11 @@
       <c r="D18">
         <v>-0.1228275137348259</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1564,6 +1819,11 @@
       <c r="D19">
         <v>0.02727041352781705</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1584,6 +1844,11 @@
       <c r="D20">
         <v>0.02076488707355596</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1604,6 +1869,11 @@
       <c r="D21">
         <v>0.006232554036223088</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1624,6 +1894,11 @@
       <c r="D22">
         <v>2.059988674213176</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1644,6 +1919,11 @@
       <c r="D23">
         <v>-0.5947632163510186</v>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1664,6 +1944,11 @@
       <c r="D24">
         <v>0.1831606239731023</v>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1684,6 +1969,11 @@
       <c r="D25">
         <v>0.159639700340937</v>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1704,6 +1994,11 @@
       <c r="D26">
         <v>0.1118253832908284</v>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1723,6 +2018,11 @@
       </c>
       <c r="D27">
         <v>-0.01806347105316433</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1732,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1756,6 +2056,11 @@
           <t>delta_pp</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cluster_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1776,6 +2081,11 @@
       <c r="D2">
         <v>6.055152015857685</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1796,6 +2106,11 @@
       <c r="D3">
         <v>-5.99987180998951</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1816,6 +2131,11 @@
       <c r="D4">
         <v>-1.927274347710815</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1836,6 +2156,11 @@
       <c r="D5">
         <v>1.521995244278301</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1856,6 +2181,11 @@
       <c r="D6">
         <v>0.4301260916707487</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1876,6 +2206,11 @@
       <c r="D7">
         <v>-0.2284832267365025</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1896,6 +2231,11 @@
       <c r="D8">
         <v>0.2215989750704636</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1916,6 +2256,11 @@
       <c r="D9">
         <v>0.2074902447874791</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1936,6 +2281,11 @@
       <c r="D10">
         <v>-0.1336855357323339</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1956,6 +2306,11 @@
       <c r="D11">
         <v>-0.1110408206044117</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1976,6 +2331,11 @@
       <c r="D12">
         <v>-0.09311114185439713</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1996,6 +2356,11 @@
       <c r="D13">
         <v>0.06227792114167248</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2016,6 +2381,11 @@
       <c r="D14">
         <v>-0.006316698939203599</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2036,6 +2406,11 @@
       <c r="D15">
         <v>0.002758267975678167</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2056,6 +2431,11 @@
       <c r="D16">
         <v>-0.00161517921485665</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Southern CCS industrial squid specialist</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2076,6 +2456,11 @@
       <c r="D17">
         <v>-4.177771891224213</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2096,6 +2481,11 @@
       <c r="D18">
         <v>3.439023115671258</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2116,6 +2506,11 @@
       <c r="D19">
         <v>0.4726493967196807</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2136,6 +2531,11 @@
       <c r="D20">
         <v>0.2959267827065523</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2156,6 +2556,11 @@
       <c r="D21">
         <v>-0.2410356559433938</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2176,6 +2581,11 @@
       <c r="D22">
         <v>0.1736366024961048</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2196,6 +2606,11 @@
       <c r="D23">
         <v>0.1258185114468804</v>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2216,6 +2631,11 @@
       <c r="D24">
         <v>-0.06501327899123002</v>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2236,6 +2656,11 @@
       <c r="D25">
         <v>-0.03891909566492886</v>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2256,6 +2681,11 @@
       <c r="D26">
         <v>0.03683172235916096</v>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2276,6 +2706,11 @@
       <c r="D27">
         <v>-0.01559369333819344</v>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2296,6 +2731,11 @@
       <c r="D28">
         <v>0.01247320770416402</v>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2316,6 +2756,11 @@
       <c r="D29">
         <v>-0.008610904258865223</v>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2336,6 +2781,11 @@
       <c r="D30">
         <v>-0.006089272116538251</v>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2356,6 +2806,11 @@
       <c r="D31">
         <v>0.005830003583613582</v>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2376,6 +2831,11 @@
       <c r="D32">
         <v>-0.004035217892375743</v>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2396,6 +2856,11 @@
       <c r="D33">
         <v>-0.003440810671121147</v>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2416,6 +2881,11 @@
       <c r="D34">
         <v>-0.001679522586552008</v>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Roving industrial squid-sardine generalist</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2436,6 +2906,11 @@
       <c r="D35">
         <v>0.6431749747037419</v>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2456,6 +2931,11 @@
       <c r="D36">
         <v>-0.3264223522766493</v>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2476,6 +2956,11 @@
       <c r="D37">
         <v>-0.2632184347319134</v>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2496,6 +2981,11 @@
       <c r="D38">
         <v>-0.1010237223809673</v>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2516,6 +3006,11 @@
       <c r="D39">
         <v>0.06302032592513056</v>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2536,6 +3031,11 @@
       <c r="D40">
         <v>-0.03218758519638507</v>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2556,6 +3056,11 @@
       <c r="D41">
         <v>0.02727041352781705</v>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2576,6 +3081,11 @@
       <c r="D42">
         <v>-0.02180379135385867</v>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2596,6 +3106,11 @@
       <c r="D43">
         <v>0.01502547140204979</v>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2616,6 +3131,11 @@
       <c r="D44">
         <v>-0.01006785365518948</v>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2636,6 +3156,11 @@
       <c r="D45">
         <v>0.006232554036223088</v>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PNW sardine specialist</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2656,6 +3181,11 @@
       <c r="D46">
         <v>2.23556643906565</v>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2676,6 +3206,11 @@
       <c r="D47">
         <v>2.02014921406027</v>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2696,6 +3231,11 @@
       <c r="D48">
         <v>-1.901787694413859</v>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2716,6 +3256,11 @@
       <c r="D49">
         <v>-1.847562055698676</v>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2736,6 +3281,11 @@
       <c r="D50">
         <v>-0.7747235336826175</v>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2756,6 +3306,11 @@
       <c r="D51">
         <v>0.4506675806695166</v>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2776,6 +3331,11 @@
       <c r="D52">
         <v>-0.1938442188063326</v>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2796,6 +3356,11 @@
       <c r="D53">
         <v>-0.1755777648524765</v>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2816,6 +3381,11 @@
       <c r="D54">
         <v>0.159639700340937</v>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2836,6 +3406,11 @@
       <c r="D55">
         <v>0.1118253832908284</v>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2856,6 +3431,11 @@
       <c r="D56">
         <v>-0.03986340786054541</v>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2876,6 +3456,11 @@
       <c r="D57">
         <v>-0.03505056872929954</v>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2896,6 +3481,11 @@
       <c r="D58">
         <v>-0.01806347105316433</v>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2916,6 +3506,11 @@
       <c r="D59">
         <v>0.007373158970007268</v>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2935,6 +3530,11 @@
       </c>
       <c r="D60">
         <v>0.001251238699763024</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Southern CCS forage fish diverse</t>
+        </is>
       </c>
     </row>
   </sheetData>
